--- a/SR数据.xlsx
+++ b/SR数据.xlsx
@@ -15,6 +15,7 @@
     <definedName name="ExternalData_1" localSheetId="2">实验数据!$A$1:$D$104</definedName>
     <definedName name="ExternalData_2" localSheetId="2">实验数据!$A$105:$D$124</definedName>
     <definedName name="ExternalData_3" localSheetId="2">实验数据!$A$126:$D$145</definedName>
+    <definedName name="ExternalData_4" localSheetId="2">实验数据!$A$146:$D$149</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
@@ -43,11 +44,18 @@
       </textFields>
     </textPr>
   </connection>
+  <connection id="4" name="result6" type="6" background="1" refreshedVersion="2" saveData="1">
+    <textPr sourceFile="D:\Audio-Kuleshov\src\checkpoints\results\result6.txt" comma="1">
+      <textFields>
+        <textField/>
+      </textFields>
+    </textPr>
+  </connection>
 </connections>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="221">
   <si>
     <t>TABLE VI</t>
   </si>
@@ -698,6 +706,18 @@
   </si>
   <si>
     <t>dnn-spec.8.mv4\eval-d\VCTK</t>
+  </si>
+  <si>
+    <t>proposed.19.MIX\eval-d\TIMIT</t>
+  </si>
+  <si>
+    <t>proposed.19.MIX\eval-d\WSJ</t>
+  </si>
+  <si>
+    <t>proposed.19.MIX\eval-d\LIBRI</t>
+  </si>
+  <si>
+    <t>proposed.19.MIX\eval-d\IEEE</t>
   </si>
 </sst>
 </file>
@@ -1473,15 +1493,19 @@
 </file>
 
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="ExternalData_3" connectionId="3" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="ExternalData_4" connectionId="4" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/queryTables/queryTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="ExternalData_1" connectionId="1" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+</file>
+
+<file path=xl/queryTables/queryTable3.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="ExternalData_2" connectionId="2" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
-<file path=xl/queryTables/queryTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="ExternalData_1" connectionId="1" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<file path=xl/queryTables/queryTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="ExternalData_3" connectionId="3" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6014,18 +6038,54 @@
       <c r="A26" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B26" s="3"/>
-      <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
-      <c r="I26" s="3"/>
-      <c r="J26" s="3"/>
-      <c r="K26" s="3"/>
-      <c r="L26" s="3"/>
-      <c r="M26" s="3"/>
+      <c r="B26" s="3">
+        <f>实验数据!B146</f>
+        <v>18.4845234060179</v>
+      </c>
+      <c r="C26" s="3">
+        <f>实验数据!C146</f>
+        <v>1.73750627040863</v>
+      </c>
+      <c r="D26" s="3">
+        <f>实验数据!D146</f>
+        <v>3.21082520484924</v>
+      </c>
+      <c r="E26" s="3">
+        <f>实验数据!B147</f>
+        <v>5.63843939661863</v>
+      </c>
+      <c r="F26" s="3">
+        <f>实验数据!C147</f>
+        <v>1.93640267848968</v>
+      </c>
+      <c r="G26" s="3">
+        <f>实验数据!D147</f>
+        <v>1.40793013572692</v>
+      </c>
+      <c r="H26" s="3">
+        <f>实验数据!B148</f>
+        <v>21.2939292728701</v>
+      </c>
+      <c r="I26" s="3">
+        <f>实验数据!C148</f>
+        <v>1.69112133979797</v>
+      </c>
+      <c r="J26" s="3">
+        <f>实验数据!D148</f>
+        <v>3.62980222702026</v>
+      </c>
+      <c r="K26" s="3">
+        <f>实验数据!B149</f>
+        <v>23.0863053044906</v>
+      </c>
+      <c r="L26" s="3">
+        <f>实验数据!C149</f>
+        <v>1.83870482444763</v>
+      </c>
+      <c r="M26" s="3">
+        <f>实验数据!D149</f>
+        <v>3.6840693950653</v>
+      </c>
       <c r="O26" s="10" t="s">
         <v>21</v>
       </c>
@@ -6137,7 +6197,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D145"/>
+  <dimension ref="A1:D149"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="42.2222222222222" customWidth="1"/>
@@ -8178,6 +8238,62 @@
         <v>2.30332899093627</v>
       </c>
     </row>
+    <row r="146" spans="1:4">
+      <c r="A146" t="s">
+        <v>217</v>
+      </c>
+      <c r="B146">
+        <v>18.4845234060179</v>
+      </c>
+      <c r="C146">
+        <v>1.73750627040863</v>
+      </c>
+      <c r="D146">
+        <v>3.21082520484924</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4">
+      <c r="A147" t="s">
+        <v>218</v>
+      </c>
+      <c r="B147">
+        <v>5.63843939661863</v>
+      </c>
+      <c r="C147">
+        <v>1.93640267848968</v>
+      </c>
+      <c r="D147">
+        <v>1.40793013572692</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4">
+      <c r="A148" t="s">
+        <v>219</v>
+      </c>
+      <c r="B148">
+        <v>21.2939292728701</v>
+      </c>
+      <c r="C148">
+        <v>1.69112133979797</v>
+      </c>
+      <c r="D148">
+        <v>3.62980222702026</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4">
+      <c r="A149" t="s">
+        <v>220</v>
+      </c>
+      <c r="B149">
+        <v>23.0863053044906</v>
+      </c>
+      <c r="C149">
+        <v>1.83870482444763</v>
+      </c>
+      <c r="D149">
+        <v>3.6840693950653</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
